--- a/data/business_matrix.xlsx
+++ b/data/business_matrix.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы ОКВЭД" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Матрица'!$A$1:$L$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,7 @@
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,7 +509,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Подсказка для промпта</t>
+          <t>Текст для клиента</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Подсказка для ML</t>
         </is>
       </c>
     </row>
@@ -563,6 +569,11 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>У компании есть кредиты. Пока ставка остаётся высокой, стоимость долга не снизится, особенно по кредитам с плавающей ставкой. Стоит проверить даты пересмотра ставок в договорах.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>У компании есть кредиты → деньги остаются дорогими, нагрузка по плавающим ставкам не снизится; проверить даты пересмотра ставок.</t>
         </is>
       </c>
@@ -618,6 +629,11 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>У компании есть лизинг. При высокой ставке новые лизинговые договоры обходятся дороже, поэтому условия для будущих сделок стоит обсудить заранее.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Лизинг привязан к стоимости денег → новые договоры дороже; имеет смысл зафиксировать условия до следующего заседания.</t>
         </is>
       </c>
@@ -673,6 +689,11 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>У компании есть депозиты. Высокая ставка позволяет получать больший доход на свободные средства, и сейчас можно зафиксировать её на более долгий срок.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>У компании есть депозиты → высокая ставка = доход на свободную ликвидность; можно зафиксировать ставку на более длинный срок.</t>
         </is>
       </c>
@@ -728,6 +749,11 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>У компании есть кредиты. Снижение ставки может открыть возможность рефинансировать долг на более выгодных условиях.</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>Снижение ставки открывает окно для рефинансирования дорогого долга.</t>
         </is>
       </c>
@@ -783,6 +809,11 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>Отрасль компании требует больших вложений. Дорогие деньги могут откладывать инвестиционные проекты как у самой компании, так и у её заказчиков.</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>Капиталоёмкая отрасль → дорогие деньги откладывают проекты как у компании, так и у её заказчиков.</t>
         </is>
       </c>
@@ -838,6 +869,11 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>Рост цен влияет на себестоимость любой компании. Сильнее всего он затрагивает бизнес с большими расходами на персонал и с долгими контрактами без индексации.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>Общий фактор для всех; вес растёт, если у компании большой ФОТ или длинные контракты без индексации.</t>
         </is>
       </c>
@@ -893,6 +929,11 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>У компании есть зарплатный проект, то есть значимый штат. Рост зарплат на рынке может увеличить расходы на персонал и осложнить удержание сотрудников.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>Есть зарплатный проект → у компании значимый штат; рост зарплат давит на расходы.</t>
         </is>
       </c>
@@ -948,6 +989,11 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>Замедление экономики может сказаться на спросе и планах продаж. Сам по себе это фоновый фактор, важнее его сочетание с новостями по отрасли.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>Фоновый фактор: важен в связке с отраслевыми новостями, сам по себе — низкий приоритет.</t>
         </is>
       </c>
@@ -1003,6 +1049,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>Компания работает в производстве или оптовой торговле. Снижение заказов в промышленности может уменьшить выручку и увеличить срок оплаты от покупателей.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>Производство/опт → снижение заказов бьёт по выручке и удлиняет оборачиваемость дебиторки.</t>
         </is>
       </c>
@@ -1058,6 +1109,11 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>Выручка компании зависит от потребительского спроса, поэтому его изменение напрямую отражается на продажах и запасах.</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>B2C-отрасль → прямое влияние на выручку; позиция банка: потребление на пике, дальше — замедление.</t>
         </is>
       </c>
@@ -1113,6 +1169,11 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>Компания ведёт внешнеэкономическую деятельность. Ослабление рубля удорожает импорт, но увеличивает рублёвую выручку от экспорта. По данным не видно, какое направление у компании основное, поэтому стоит оценить оба сценария.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>ВАЖНО: данные ФТС не говорят, импорт это или экспорт → агент даёт оба сценария (импортёр: дороже закупки; экспортёр: больше рублёвой выручки).</t>
         </is>
       </c>
@@ -1168,6 +1229,11 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>Компания ведёт внешнеэкономическую деятельность. Укрепление рубля удешевляет импорт, но снижает рублёвую выручку от экспорта. Стоит оценить оба сценария.</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>Зеркально FX_RUB_WEAK; без данных о направлении ВЭД — два сценария.</t>
         </is>
       </c>
@@ -1223,6 +1289,11 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
+          <t>Компания работает с Китаем. Курс и доступность юаня напрямую влияют на стоимость и сроки расчётов с партнёрами.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>ВЭД с Китаем → прямой канал влияния: курс и доступность юаня меняют стоимость и сроки расчётов.</t>
         </is>
       </c>
@@ -1278,6 +1349,11 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>Компания ведёт внешнеэкономическую деятельность, поэтому изменения санкционного режима могут затронуть её платежи, логистику и контрагентов. Стоит проверить, касаются ли меры конкретных стран, товаров и партнёров.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>Вес повышается, если страна ФТС упомянута в новости. Рекомендации — только проверка и комплаенс, без советов по обходу ограничений.</t>
         </is>
       </c>
@@ -1333,6 +1409,11 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>Компания ведёт внешнеэкономическую деятельность. Изменение пошлин и таможенных правил прямо влияет на стоимость ввозимых товаров и сроки поставок.</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>ВЭД-компания → изменения пошлин напрямую меняют себестоимость.</t>
         </is>
       </c>
@@ -1388,6 +1469,11 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t>В отрасли компании заметная доля затрат приходится на топливо. Изменения на рынке дизеля могут отразиться на расходах, но эффект нужно сверить с собственными затратами.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>Топливоёмкая отрасль → рост цен на дизель прямо в себестоимости.</t>
         </is>
       </c>
@@ -1443,6 +1529,11 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
+          <t>Компания работает в нефтегазовой отрасли, поэтому цена нефти напрямую влияет на её выручку и налоговую нагрузку.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>Нефтегаз → цена нефти = выручка; для остальных — только косвенно через курс и бюджет.</t>
         </is>
       </c>
@@ -1498,6 +1589,11 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>Металлы — заметная часть затрат или выручки в отрасли компании. Эффект от изменения цен зависит от того, покупает компания металл или производит его.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>Направление влияния зависит от того, производит компания металл или потребляет его.</t>
         </is>
       </c>
@@ -1553,6 +1649,11 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
+          <t>Деятельность компании связана с золотом, поэтому изменение его цены напрямую влияет на выручку или стоимость сырья.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>Золотодобыча/ювелирка → прямое влияние; для остальных золото не релевантно.</t>
         </is>
       </c>
@@ -1608,6 +1709,11 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t>Компания работает в строительстве или недвижимости. Условия ипотеки — один из главных факторов спроса на её продукцию.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>Стройка/девелопмент → ипотека = основной канал спроса.</t>
         </is>
       </c>
@@ -1663,6 +1769,11 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
+          <t>У компании есть банковские гарантии, такие часто используются в госзакупках. Если компания работает с госзаказчиками, изменение бюджетных расходов может повлиять на её выручку.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>Есть гарантии → вероятна работа с госзаказом; уточнить в ответе как гипотезу, не факт.</t>
         </is>
       </c>
@@ -1718,6 +1829,11 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t>Компания достаточно крупная, чтобы рассматривать выпуск облигаций как альтернативу кредиту. Ситуация на долговом рынке определяет стоимость такого заимствования.</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>Только для очень крупных компаний (≥50 млрд): облигации как альтернатива кредиту.</t>
         </is>
       </c>
@@ -1773,6 +1889,11 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
+          <t>Один из ключевых контрагентов компании работает в отрасли, которой касается новость. Проблемы партнёра могут привести к задержкам оплаты или поставок.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>Вес умножается на долю этого контрагента в платежах компании (см. лист «Скоринг»).</t>
         </is>
       </c>
@@ -1828,6 +1949,11 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
+          <t>Больше 30% закупок компании приходится на одного поставщика. Любой сбой у него или в его отрасли может нарушить поставки.</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>Один поставщик ≥30% закупок → любой сбой в его отрасли критичен.</t>
         </is>
       </c>
@@ -1883,12 +2009,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
+          <t>Больше 30% выручки компании приходится на одного покупателя. Его трудности могут прямо сказаться на выручке и сроках оплаты.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>Один покупатель ≥30% выручки → его проблемы = проблемы компании.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K26"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
